--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>121291143</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291200</v>
+        <v>121291182</v>
       </c>
       <c r="B7" t="n">
-        <v>56560</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,50 +1241,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767939</v>
+        <v>767692</v>
       </c>
       <c r="R7" t="n">
-        <v>7095758</v>
+        <v>7096019</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291182</v>
+        <v>121291102</v>
       </c>
       <c r="B8" t="n">
-        <v>57501</v>
+        <v>57367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,46 +1359,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767692</v>
+        <v>767714</v>
       </c>
       <c r="R8" t="n">
-        <v>7096019</v>
+        <v>7095342</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291102</v>
+        <v>121291168</v>
       </c>
       <c r="B9" t="n">
-        <v>57364</v>
+        <v>90084</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,46 +1465,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767714</v>
+        <v>767627</v>
       </c>
       <c r="R9" t="n">
-        <v>7095342</v>
+        <v>7096035</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,6 +1540,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291106</v>
+        <v>121291200</v>
       </c>
       <c r="B10" t="n">
-        <v>82382</v>
+        <v>56563</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,30 +1571,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1610,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767726</v>
+        <v>767939</v>
       </c>
       <c r="R10" t="n">
-        <v>7095354</v>
+        <v>7095758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,7 +1655,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121291123</v>
+        <v>121291106</v>
       </c>
       <c r="B11" t="n">
-        <v>57364</v>
+        <v>82385</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,31 +1689,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1721,10 +1716,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767640</v>
+        <v>767726</v>
       </c>
       <c r="R11" t="n">
-        <v>7095334</v>
+        <v>7095354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,6 +1760,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1783,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121291168</v>
+        <v>121291123</v>
       </c>
       <c r="B12" t="n">
-        <v>90074</v>
+        <v>57367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,41 +1791,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767627</v>
+        <v>767640</v>
       </c>
       <c r="R12" t="n">
-        <v>7096035</v>
+        <v>7095334</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1871,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291143</v>
+        <v>121291168</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>90084</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,14 +1162,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767726</v>
+        <v>767627</v>
       </c>
       <c r="R6" t="n">
-        <v>7095916</v>
+        <v>7096035</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291182</v>
+        <v>121291143</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,46 +1245,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767692</v>
+        <v>767726</v>
       </c>
       <c r="R7" t="n">
-        <v>7096019</v>
+        <v>7095916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,6 +1316,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1343,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291102</v>
+        <v>121291200</v>
       </c>
       <c r="B8" t="n">
-        <v>57367</v>
+        <v>56563</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,35 +1347,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767714</v>
+        <v>767939</v>
       </c>
       <c r="R8" t="n">
-        <v>7095342</v>
+        <v>7095758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291168</v>
+        <v>121291102</v>
       </c>
       <c r="B9" t="n">
-        <v>90084</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,41 +1461,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767627</v>
+        <v>767714</v>
       </c>
       <c r="R9" t="n">
-        <v>7096035</v>
+        <v>7095342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1541,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291200</v>
+        <v>121291106</v>
       </c>
       <c r="B10" t="n">
-        <v>56563</v>
+        <v>82385</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,39 +1571,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1611,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767939</v>
+        <v>767726</v>
       </c>
       <c r="R10" t="n">
-        <v>7095758</v>
+        <v>7095354</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,6 +1646,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1673,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121291106</v>
+        <v>121291123</v>
       </c>
       <c r="B11" t="n">
-        <v>82385</v>
+        <v>57367</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,26 +1681,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1716,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767726</v>
+        <v>767640</v>
       </c>
       <c r="R11" t="n">
-        <v>7095354</v>
+        <v>7095334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,7 +1757,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1779,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121291123</v>
+        <v>121291182</v>
       </c>
       <c r="B12" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,42 +1791,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767640</v>
+        <v>767692</v>
       </c>
       <c r="R12" t="n">
-        <v>7095334</v>
+        <v>7096019</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291168</v>
+        <v>121291106</v>
       </c>
       <c r="B6" t="n">
-        <v>90084</v>
+        <v>82388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,14 +1162,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767627</v>
+        <v>767726</v>
       </c>
       <c r="R6" t="n">
-        <v>7096035</v>
+        <v>7095354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291143</v>
+        <v>121291102</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,26 +1245,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1272,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767726</v>
+        <v>767714</v>
       </c>
       <c r="R7" t="n">
-        <v>7095916</v>
+        <v>7095342</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,7 +1321,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291200</v>
+        <v>121291143</v>
       </c>
       <c r="B8" t="n">
-        <v>56563</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,39 +1351,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1387,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767939</v>
+        <v>767726</v>
       </c>
       <c r="R8" t="n">
-        <v>7095758</v>
+        <v>7095916</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,6 +1426,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1449,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291102</v>
+        <v>121291168</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>90092</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,46 +1457,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767714</v>
+        <v>767627</v>
       </c>
       <c r="R9" t="n">
-        <v>7095342</v>
+        <v>7096035</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,6 +1532,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1559,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291106</v>
+        <v>121291200</v>
       </c>
       <c r="B10" t="n">
-        <v>82385</v>
+        <v>56563</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,30 +1563,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1602,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767726</v>
+        <v>767939</v>
       </c>
       <c r="R10" t="n">
-        <v>7095354</v>
+        <v>7095758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1647,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291106</v>
+        <v>121291200</v>
       </c>
       <c r="B6" t="n">
-        <v>82388</v>
+        <v>56563</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,30 +1135,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1166,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767726</v>
+        <v>767939</v>
       </c>
       <c r="R6" t="n">
-        <v>7095354</v>
+        <v>7095758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1219,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1229,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291102</v>
+        <v>121291143</v>
       </c>
       <c r="B7" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,31 +1253,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1277,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767714</v>
+        <v>767726</v>
       </c>
       <c r="R7" t="n">
-        <v>7095342</v>
+        <v>7095916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,6 +1324,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1339,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291143</v>
+        <v>121291123</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>57367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,26 +1359,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1382,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767726</v>
+        <v>767640</v>
       </c>
       <c r="R8" t="n">
-        <v>7095916</v>
+        <v>7095334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1435,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1445,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291168</v>
+        <v>121291182</v>
       </c>
       <c r="B9" t="n">
-        <v>90092</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,30 +1465,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5685</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1488,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767627</v>
+        <v>767692</v>
       </c>
       <c r="R9" t="n">
-        <v>7096035</v>
+        <v>7096019</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1549,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1551,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291200</v>
+        <v>121291106</v>
       </c>
       <c r="B10" t="n">
-        <v>56563</v>
+        <v>82388</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,39 +1579,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1603,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767939</v>
+        <v>767726</v>
       </c>
       <c r="R10" t="n">
-        <v>7095758</v>
+        <v>7095354</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,6 +1654,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1665,7 +1673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121291123</v>
+        <v>121291102</v>
       </c>
       <c r="B11" t="n">
         <v>57367</v>
@@ -1713,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767640</v>
+        <v>767714</v>
       </c>
       <c r="R11" t="n">
-        <v>7095334</v>
+        <v>7095342</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,10 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121291182</v>
+        <v>121291168</v>
       </c>
       <c r="B12" t="n">
-        <v>57504</v>
+        <v>90093</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,39 +1795,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1827,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767692</v>
+        <v>767627</v>
       </c>
       <c r="R12" t="n">
-        <v>7096019</v>
+        <v>7096035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,6 +1870,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291200</v>
+        <v>121291102</v>
       </c>
       <c r="B6" t="n">
-        <v>56563</v>
+        <v>57370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,39 +1135,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767939</v>
+        <v>767714</v>
       </c>
       <c r="R6" t="n">
-        <v>7095758</v>
+        <v>7095342</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291143</v>
+        <v>121291200</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>56566</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,30 +1245,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767726</v>
+        <v>767939</v>
       </c>
       <c r="R7" t="n">
-        <v>7095916</v>
+        <v>7095758</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1343,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291123</v>
+        <v>121291182</v>
       </c>
       <c r="B8" t="n">
-        <v>57367</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,42 +1363,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767640</v>
+        <v>767692</v>
       </c>
       <c r="R8" t="n">
-        <v>7095334</v>
+        <v>7096019</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291182</v>
+        <v>121291106</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>82391</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,46 +1477,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767692</v>
+        <v>767726</v>
       </c>
       <c r="R9" t="n">
-        <v>7096019</v>
+        <v>7095354</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,6 +1548,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291106</v>
+        <v>121291143</v>
       </c>
       <c r="B10" t="n">
-        <v>82388</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,21 +1583,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,7 +1613,7 @@
         <v>767726</v>
       </c>
       <c r="R10" t="n">
-        <v>7095354</v>
+        <v>7095916</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121291102</v>
+        <v>121291123</v>
       </c>
       <c r="B11" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767714</v>
+        <v>767640</v>
       </c>
       <c r="R11" t="n">
-        <v>7095342</v>
+        <v>7095334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1786,7 @@
         <v>121291168</v>
       </c>
       <c r="B12" t="n">
-        <v>90093</v>
+        <v>90096</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291102</v>
+        <v>121291123</v>
       </c>
       <c r="B6" t="n">
         <v>57370</v>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767714</v>
+        <v>767640</v>
       </c>
       <c r="R6" t="n">
-        <v>7095342</v>
+        <v>7095334</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291200</v>
+        <v>121291102</v>
       </c>
       <c r="B7" t="n">
-        <v>56566</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,39 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767939</v>
+        <v>767714</v>
       </c>
       <c r="R7" t="n">
-        <v>7095758</v>
+        <v>7095342</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291182</v>
+        <v>121291106</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>82391</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,46 +1359,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767692</v>
+        <v>767726</v>
       </c>
       <c r="R8" t="n">
-        <v>7096019</v>
+        <v>7095354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,6 +1430,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1461,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291106</v>
+        <v>121291143</v>
       </c>
       <c r="B9" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,7 +1495,7 @@
         <v>767726</v>
       </c>
       <c r="R9" t="n">
-        <v>7095354</v>
+        <v>7095916</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291143</v>
+        <v>121291182</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,37 +1571,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767726</v>
+        <v>767692</v>
       </c>
       <c r="R10" t="n">
-        <v>7095916</v>
+        <v>7096019</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,7 +1651,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1673,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121291123</v>
+        <v>121291200</v>
       </c>
       <c r="B11" t="n">
-        <v>57370</v>
+        <v>56566</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,35 +1681,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767640</v>
+        <v>767939</v>
       </c>
       <c r="R11" t="n">
-        <v>7095334</v>
+        <v>7095758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291106</v>
+        <v>121291182</v>
       </c>
       <c r="B8" t="n">
-        <v>82391</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,37 +1359,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767726</v>
+        <v>767692</v>
       </c>
       <c r="R8" t="n">
-        <v>7095354</v>
+        <v>7096019</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1439,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1449,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291143</v>
+        <v>121291106</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>82391</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,21 +1473,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,7 +1503,7 @@
         <v>767726</v>
       </c>
       <c r="R9" t="n">
-        <v>7095916</v>
+        <v>7095354</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291182</v>
+        <v>121291143</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,46 +1579,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767692</v>
+        <v>767726</v>
       </c>
       <c r="R10" t="n">
-        <v>7096019</v>
+        <v>7095916</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,6 +1650,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291182</v>
+        <v>121291106</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>82391</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,46 +1359,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767692</v>
+        <v>767726</v>
       </c>
       <c r="R8" t="n">
-        <v>7096019</v>
+        <v>7095354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,6 +1430,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1457,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291106</v>
+        <v>121291143</v>
       </c>
       <c r="B9" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,7 +1495,7 @@
         <v>767726</v>
       </c>
       <c r="R9" t="n">
-        <v>7095354</v>
+        <v>7095916</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291143</v>
+        <v>121291182</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,37 +1571,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767726</v>
+        <v>767692</v>
       </c>
       <c r="R10" t="n">
-        <v>7095916</v>
+        <v>7096019</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1651,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291123</v>
+        <v>121291182</v>
       </c>
       <c r="B6" t="n">
-        <v>57370</v>
+        <v>57508</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,42 +1139,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767640</v>
+        <v>767692</v>
       </c>
       <c r="R6" t="n">
-        <v>7095334</v>
+        <v>7096019</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291102</v>
+        <v>121291200</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>56567</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,35 +1249,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767714</v>
+        <v>767939</v>
       </c>
       <c r="R7" t="n">
-        <v>7095342</v>
+        <v>7095758</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291106</v>
+        <v>121291123</v>
       </c>
       <c r="B8" t="n">
-        <v>82391</v>
+        <v>57371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,26 +1367,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1386,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767726</v>
+        <v>767640</v>
       </c>
       <c r="R8" t="n">
-        <v>7095354</v>
+        <v>7095334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1443,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1449,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291143</v>
+        <v>121291102</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>57371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,26 +1477,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1492,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767726</v>
+        <v>767714</v>
       </c>
       <c r="R9" t="n">
-        <v>7095916</v>
+        <v>7095342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1553,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1555,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291182</v>
+        <v>121291106</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>82392</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,46 +1587,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767692</v>
+        <v>767726</v>
       </c>
       <c r="R10" t="n">
-        <v>7096019</v>
+        <v>7095354</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,6 +1658,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1669,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121291200</v>
+        <v>121291168</v>
       </c>
       <c r="B11" t="n">
-        <v>56566</v>
+        <v>90102</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,46 +1693,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>5685</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767939</v>
+        <v>767627</v>
       </c>
       <c r="R11" t="n">
-        <v>7095758</v>
+        <v>7096035</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,6 +1764,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121291168</v>
+        <v>121291143</v>
       </c>
       <c r="B12" t="n">
-        <v>90096</v>
+        <v>78608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,25 +1795,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1822,14 +1822,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767627</v>
+        <v>767726</v>
       </c>
       <c r="R12" t="n">
-        <v>7096035</v>
+        <v>7095916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291182</v>
+        <v>121291106</v>
       </c>
       <c r="B6" t="n">
-        <v>57508</v>
+        <v>82393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,46 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767692</v>
+        <v>767726</v>
       </c>
       <c r="R6" t="n">
-        <v>7096019</v>
+        <v>7095354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,6 +1210,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291200</v>
+        <v>121291182</v>
       </c>
       <c r="B7" t="n">
-        <v>56567</v>
+        <v>57509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,50 +1241,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767939</v>
+        <v>767692</v>
       </c>
       <c r="R7" t="n">
-        <v>7095758</v>
+        <v>7096019</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1346,7 @@
         <v>121291123</v>
       </c>
       <c r="B8" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1461,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291102</v>
+        <v>121291168</v>
       </c>
       <c r="B9" t="n">
-        <v>57371</v>
+        <v>90103</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,46 +1465,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767714</v>
+        <v>767627</v>
       </c>
       <c r="R9" t="n">
-        <v>7095342</v>
+        <v>7096035</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,6 +1540,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1571,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291106</v>
+        <v>121291143</v>
       </c>
       <c r="B10" t="n">
-        <v>82392</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,7 +1605,7 @@
         <v>767726</v>
       </c>
       <c r="R10" t="n">
-        <v>7095354</v>
+        <v>7095916</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121291168</v>
+        <v>121291102</v>
       </c>
       <c r="B11" t="n">
-        <v>90102</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,41 +1677,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767627</v>
+        <v>767714</v>
       </c>
       <c r="R11" t="n">
-        <v>7096035</v>
+        <v>7095342</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1764,7 +1757,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1783,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121291143</v>
+        <v>121291200</v>
       </c>
       <c r="B12" t="n">
-        <v>78608</v>
+        <v>56568</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,30 +1787,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1826,10 +1827,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767726</v>
+        <v>767939</v>
       </c>
       <c r="R12" t="n">
-        <v>7095916</v>
+        <v>7095758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1871,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291106</v>
+        <v>121291200</v>
       </c>
       <c r="B6" t="n">
-        <v>82393</v>
+        <v>56568</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,30 +1135,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1166,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767726</v>
+        <v>767939</v>
       </c>
       <c r="R6" t="n">
-        <v>7095354</v>
+        <v>7095758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1219,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1229,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291182</v>
+        <v>121291143</v>
       </c>
       <c r="B7" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,46 +1253,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767692</v>
+        <v>767726</v>
       </c>
       <c r="R7" t="n">
-        <v>7096019</v>
+        <v>7095916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,6 +1324,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291143</v>
+        <v>121291182</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,37 +1575,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767726</v>
+        <v>767692</v>
       </c>
       <c r="R10" t="n">
-        <v>7095916</v>
+        <v>7096019</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1655,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1775,10 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121291200</v>
+        <v>121291106</v>
       </c>
       <c r="B12" t="n">
-        <v>56568</v>
+        <v>82393</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,39 +1795,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1827,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767939</v>
+        <v>767726</v>
       </c>
       <c r="R12" t="n">
-        <v>7095758</v>
+        <v>7095354</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,6 +1870,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291200</v>
+        <v>121291182</v>
       </c>
       <c r="B6" t="n">
-        <v>56568</v>
+        <v>57509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,50 +1135,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767939</v>
+        <v>767692</v>
       </c>
       <c r="R6" t="n">
-        <v>7095758</v>
+        <v>7096019</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291143</v>
+        <v>121291102</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,26 +1253,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767726</v>
+        <v>767714</v>
       </c>
       <c r="R7" t="n">
-        <v>7095916</v>
+        <v>7095342</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1343,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291123</v>
+        <v>121291106</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>82393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,31 +1363,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767640</v>
+        <v>767726</v>
       </c>
       <c r="R8" t="n">
-        <v>7095334</v>
+        <v>7095354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,6 +1434,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291168</v>
+        <v>121291200</v>
       </c>
       <c r="B9" t="n">
-        <v>90103</v>
+        <v>56568</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,37 +1469,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5685</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767627</v>
+        <v>767939</v>
       </c>
       <c r="R9" t="n">
-        <v>7096035</v>
+        <v>7095758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1549,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1559,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121291182</v>
+        <v>121291143</v>
       </c>
       <c r="B10" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,46 +1583,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>767692</v>
+        <v>767726</v>
       </c>
       <c r="R10" t="n">
-        <v>7096019</v>
+        <v>7095916</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,6 +1654,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121291102</v>
+        <v>121291123</v>
       </c>
       <c r="B11" t="n">
         <v>57372</v>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767714</v>
+        <v>767640</v>
       </c>
       <c r="R11" t="n">
-        <v>7095342</v>
+        <v>7095334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121291106</v>
+        <v>121291168</v>
       </c>
       <c r="B12" t="n">
-        <v>82393</v>
+        <v>90103</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,25 +1795,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>5685</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1822,14 +1822,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767726</v>
+        <v>767627</v>
       </c>
       <c r="R12" t="n">
-        <v>7095354</v>
+        <v>7096035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291182</v>
+        <v>121291168</v>
       </c>
       <c r="B6" t="n">
-        <v>57509</v>
+        <v>90103</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,39 +1135,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767692</v>
+        <v>767627</v>
       </c>
       <c r="R6" t="n">
-        <v>7096019</v>
+        <v>7096035</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,6 +1210,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291102</v>
+        <v>121291106</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>82393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,31 +1245,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767714</v>
+        <v>767726</v>
       </c>
       <c r="R7" t="n">
-        <v>7095342</v>
+        <v>7095354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,6 +1316,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291106</v>
+        <v>121291102</v>
       </c>
       <c r="B8" t="n">
-        <v>82393</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,26 +1351,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1390,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767726</v>
+        <v>767714</v>
       </c>
       <c r="R8" t="n">
-        <v>7095354</v>
+        <v>7095342</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1427,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1453,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291200</v>
+        <v>121291123</v>
       </c>
       <c r="B9" t="n">
-        <v>56568</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,39 +1457,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1505,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>767939</v>
+        <v>767640</v>
       </c>
       <c r="R9" t="n">
-        <v>7095758</v>
+        <v>7095334</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1673,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121291123</v>
+        <v>121291182</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,42 +1677,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>767640</v>
+        <v>767692</v>
       </c>
       <c r="R11" t="n">
-        <v>7095334</v>
+        <v>7096019</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121291168</v>
+        <v>121291200</v>
       </c>
       <c r="B12" t="n">
-        <v>90103</v>
+        <v>56568</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1799,37 +1791,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5685</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>767627</v>
+        <v>767939</v>
       </c>
       <c r="R12" t="n">
-        <v>7096035</v>
+        <v>7095758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1871,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49036-2024 artfynd.xlsx
+++ b/artfynd/A 49036-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291168</v>
+        <v>121291106</v>
       </c>
       <c r="B6" t="n">
-        <v>90103</v>
+        <v>82393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,14 +1162,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsjön, Vb</t>
+          <t>Långsjöberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767627</v>
+        <v>767726</v>
       </c>
       <c r="R6" t="n">
-        <v>7096035</v>
+        <v>7095354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291106</v>
+        <v>121291168</v>
       </c>
       <c r="B7" t="n">
-        <v>82393</v>
+        <v>90103</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,25 +1241,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5685</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,14 +1268,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långsjöberget, Vb</t>
+          <t>Långsjön, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767726</v>
+        <v>767627</v>
       </c>
       <c r="R7" t="n">
-        <v>7095354</v>
+        <v>7096035</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
